--- a/ig/nr-fix-typo/ValueSet-fr-core-encounter-class.xlsx
+++ b/ig/nr-fix-typo/ValueSet-fr-core-encounter-class.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T12:59:19+00:00</t>
+    <t>2023-11-06T14:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
